--- a/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
+++ b/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/GenIA/Normativo/LexIA_Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="287" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B013D15-DD81-4739-9214-2327C814D018}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAE6CAA8-09D5-4A19-B12F-52726A29477B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2444" uniqueCount="954">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="968">
   <si>
     <t>Dia</t>
   </si>
@@ -2858,6 +2858,48 @@
   </si>
   <si>
     <t>Modifican la Res. N° 000049-2026/SUNAT a fin de otorgar plazo adicional a los sujetos obligados a utilizar el programa para el envío de información a la SUNAT denominado PEI - WEB para su adecuada implementación</t>
+  </si>
+  <si>
+    <t>Nº D000012-2026-RENIEC-JNAC</t>
+  </si>
+  <si>
+    <t>Aprueban los “Lineamientos para la emisión y uso del Documento Nacional de Identidad digital (DNId)”</t>
+  </si>
+  <si>
+    <t>Nº 175-2026-INEI</t>
+  </si>
+  <si>
+    <t>Índices de Precios al Consumidor a Nivel Nacional y de Lima Metropolitana, correspondientes al mes de julio 2026</t>
+  </si>
+  <si>
+    <t>Nº 176-2026-INEI</t>
+  </si>
+  <si>
+    <t>Índice de Precios al Por Mayor a Nivel Nacional, correspondiente al mes de julio de 2026</t>
+  </si>
+  <si>
+    <t>Nº 0019-2026-BCRP</t>
+  </si>
+  <si>
+    <t>Índice de reajuste diario a que se refiere el artículo 240º de la Ley General del Sistema Financiero y del Sistema de Seguros, correspondiente al mes de agosto de 2026</t>
+  </si>
+  <si>
+    <t>SBS N° 01959-2026</t>
+  </si>
+  <si>
+    <t>Modifican Reglamento de Gobierno Corporativo y de la Gestión Integral de Riesgos, aprobado por la Resolución SBS Nº 272-2017 y sus modificatorias</t>
+  </si>
+  <si>
+    <t>N° 01960-2026-SBS</t>
+  </si>
+  <si>
+    <t>Modifican Normas para la cobertura, recursos y pago de imposiciones cubiertas del Fondo de Seguro de Depósitos</t>
+  </si>
+  <si>
+    <t>Nº 332-2026-EF/15</t>
+  </si>
+  <si>
+    <t>Modifican el Reglamento Operativo del Programa Impulso Empresarial MYPE – IMPULSO MYPERU</t>
   </si>
   <si>
     <t>IDENTIFICÓ LA NORMA DE INTERÉS</t>
@@ -12993,6 +13035,146 @@
         <v>927</v>
       </c>
     </row>
+    <row r="457" spans="1:6">
+      <c r="A457" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B457" t="s">
+        <v>49</v>
+      </c>
+      <c r="C457" t="s">
+        <v>928</v>
+      </c>
+      <c r="D457" t="s">
+        <v>29</v>
+      </c>
+      <c r="E457" t="s">
+        <v>835</v>
+      </c>
+      <c r="F457" s="4" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
+      <c r="A458" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B458" t="s">
+        <v>49</v>
+      </c>
+      <c r="C458" t="s">
+        <v>930</v>
+      </c>
+      <c r="D458" t="s">
+        <v>29</v>
+      </c>
+      <c r="E458" t="s">
+        <v>30</v>
+      </c>
+      <c r="F458" s="4" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
+      <c r="A459" s="3">
+        <v>46235</v>
+      </c>
+      <c r="B459" t="s">
+        <v>49</v>
+      </c>
+      <c r="C459" t="s">
+        <v>932</v>
+      </c>
+      <c r="D459" t="s">
+        <v>29</v>
+      </c>
+      <c r="E459" t="s">
+        <v>30</v>
+      </c>
+      <c r="F459" s="4" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
+      <c r="A460" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B460" t="s">
+        <v>86</v>
+      </c>
+      <c r="C460" t="s">
+        <v>934</v>
+      </c>
+      <c r="D460" t="s">
+        <v>29</v>
+      </c>
+      <c r="E460" t="s">
+        <v>840</v>
+      </c>
+      <c r="F460" s="4" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
+      <c r="A461" s="3">
+        <v>46238</v>
+      </c>
+      <c r="B461" t="s">
+        <v>49</v>
+      </c>
+      <c r="C461" t="s">
+        <v>936</v>
+      </c>
+      <c r="D461" t="s">
+        <v>29</v>
+      </c>
+      <c r="E461" t="s">
+        <v>835</v>
+      </c>
+      <c r="F461" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
+      <c r="A462" s="3">
+        <v>46239</v>
+      </c>
+      <c r="B462" t="s">
+        <v>49</v>
+      </c>
+      <c r="C462" t="s">
+        <v>938</v>
+      </c>
+      <c r="D462" t="s">
+        <v>29</v>
+      </c>
+      <c r="E462" t="s">
+        <v>840</v>
+      </c>
+      <c r="F462" s="4" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
+      <c r="A463" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B463" t="s">
+        <v>49</v>
+      </c>
+      <c r="C463" t="s">
+        <v>940</v>
+      </c>
+      <c r="D463" t="s">
+        <v>29</v>
+      </c>
+      <c r="E463" t="s">
+        <v>840</v>
+      </c>
+      <c r="F463" s="4" t="s">
+        <v>941</v>
+      </c>
+    </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
     <row r="1048574" ht="12.75" customHeight="1"/>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -13017,7 +13199,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="D2" s="34" t="s">
-        <v>928</v>
+        <v>942</v>
       </c>
       <c r="E2" s="34"/>
     </row>
@@ -13026,10 +13208,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>929</v>
+        <v>943</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>930</v>
+        <v>944</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>24</v>
@@ -13038,44 +13220,44 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>932</v>
+        <v>946</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="362.45">
       <c r="B4" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="304.5">
       <c r="B5" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13087,18 +13269,18 @@
         <v>31</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>29</v>
@@ -13110,18 +13292,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>29</v>
@@ -13133,15 +13315,15 @@
         <v>37</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="12" t="s">
@@ -13157,10 +13339,10 @@
     </row>
     <row r="9" spans="2:8" ht="409.5">
       <c r="B9" s="12" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="12" t="s">
@@ -13176,13 +13358,13 @@
     </row>
     <row r="10" spans="2:8" ht="409.5">
       <c r="B10" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -13197,55 +13379,55 @@
     </row>
     <row r="11" spans="2:8" ht="275.45">
       <c r="B11" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="H11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="188.45">
       <c r="B12" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C12" s="11" t="s">
+        <v>963</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>935</v>
-      </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="H12" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="409.5">
       <c r="B13" s="12" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
@@ -13254,7 +13436,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>953</v>
+        <v>967</v>
       </c>
       <c r="H13" s="42"/>
     </row>
@@ -13272,36 +13454,36 @@
   <sheetData>
     <row r="2" spans="2:8" ht="362.45">
       <c r="B2" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>934</v>
+        <v>948</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>936</v>
+        <v>950</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>937</v>
+        <v>951</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="304.5">
       <c r="B3" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>938</v>
+        <v>952</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>29</v>
@@ -13313,18 +13495,18 @@
         <v>31</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="409.5">
       <c r="B4" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>940</v>
+        <v>954</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>29</v>
@@ -13336,18 +13518,18 @@
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="409.5">
       <c r="B5" s="12" t="s">
-        <v>933</v>
+        <v>947</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>941</v>
+        <v>955</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13359,15 +13541,15 @@
         <v>37</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>939</v>
+        <v>953</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>943</v>
+        <v>957</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="12" t="s">
@@ -13383,10 +13565,10 @@
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>942</v>
+        <v>956</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>944</v>
+        <v>958</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="12" t="s">
@@ -13402,13 +13584,13 @@
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>946</v>
+        <v>960</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>29</v>
@@ -13423,55 +13605,55 @@
     </row>
     <row r="9" spans="2:8" ht="275.45">
       <c r="B9" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>947</v>
+        <v>961</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>948</v>
+        <v>962</v>
       </c>
       <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="188.45">
       <c r="B10" s="12" t="s">
-        <v>945</v>
+        <v>959</v>
       </c>
       <c r="C10" s="11" t="s">
+        <v>963</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="12" t="s">
         <v>949</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>935</v>
-      </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>950</v>
+        <v>964</v>
       </c>
       <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="409.5">
       <c r="B11" s="12" t="s">
-        <v>951</v>
+        <v>965</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>952</v>
+        <v>966</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
@@ -13480,7 +13662,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>953</v>
+        <v>967</v>
       </c>
       <c r="H11" s="42"/>
     </row>

--- a/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
+++ b/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/GenIA/Normativo/LexIA_Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAE6CAA8-09D5-4A19-B12F-52726A29477B}"/>
+  <xr:revisionPtr revIDLastSave="354" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C6455B-6FAC-4842-8952-D3366FFEB454}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2479" uniqueCount="968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="974">
   <si>
     <t>Dia</t>
   </si>
@@ -2900,6 +2900,26 @@
   </si>
   <si>
     <t>Modifican el Reglamento Operativo del Programa Impulso Empresarial MYPE – IMPULSO MYPERU</t>
+  </si>
+  <si>
+    <t>Nº 115-2026-PCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decreto Supremo que declara el Estado de Emergencia en algunos distritos de las provincias de Huancavelica y Tayacaja del departamento de Huancavelica y de
+las provincias de Chupaca, Concepción y Huancayo del departamento de Junín, por impacto de daños a consecuencia de movimientos sísmicos </t>
+  </si>
+  <si>
+    <t>Nº 116-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el Estado de Emergencia en varios distritos de algunas provincias de los departamentos de Apurímac, Arequipa, Ayacucho, Cusco,
+Huancavelica, Huánuco, Junín, La Libertad, Loreto, Madre De Dios, Moquegua, Pasco, Puno, San Martín, Tacna y Ucayali, por peligro inminente ante déficit hídrico para el período de lluvias 2026-2027</t>
+  </si>
+  <si>
+    <t>SBS N° 02027-2026</t>
+  </si>
+  <si>
+    <t>Modifican la Resolución SBS N° 04131-2025 y el Reglamento de Notificación vía Casilla Electrónica de la SBS</t>
   </si>
   <si>
     <t>IDENTIFICÓ LA NORMA DE INTERÉS</t>
@@ -13175,6 +13195,66 @@
         <v>941</v>
       </c>
     </row>
+    <row r="464" spans="1:6" ht="57.75">
+      <c r="A464" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B464" t="s">
+        <v>46</v>
+      </c>
+      <c r="C464" t="s">
+        <v>942</v>
+      </c>
+      <c r="D464" t="s">
+        <v>29</v>
+      </c>
+      <c r="E464" t="s">
+        <v>30</v>
+      </c>
+      <c r="F464" s="45" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6" ht="87">
+      <c r="A465" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B465" t="s">
+        <v>46</v>
+      </c>
+      <c r="C465" t="s">
+        <v>944</v>
+      </c>
+      <c r="D465" t="s">
+        <v>29</v>
+      </c>
+      <c r="E465" t="s">
+        <v>30</v>
+      </c>
+      <c r="F465" s="45" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
+      <c r="A466" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B466" t="s">
+        <v>49</v>
+      </c>
+      <c r="C466" t="s">
+        <v>946</v>
+      </c>
+      <c r="D466" t="s">
+        <v>29</v>
+      </c>
+      <c r="E466" t="s">
+        <v>30</v>
+      </c>
+      <c r="F466" s="4" t="s">
+        <v>947</v>
+      </c>
+    </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
     <row r="1048574" ht="12.75" customHeight="1"/>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -13199,7 +13279,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="D2" s="34" t="s">
-        <v>942</v>
+        <v>948</v>
       </c>
       <c r="E2" s="34"/>
     </row>
@@ -13208,10 +13288,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>943</v>
+        <v>949</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>944</v>
+        <v>950</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>24</v>
@@ -13220,44 +13300,44 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>945</v>
+        <v>951</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>946</v>
+        <v>952</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="362.45">
       <c r="B4" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="304.5">
       <c r="B5" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13269,18 +13349,18 @@
         <v>31</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>29</v>
@@ -13292,18 +13372,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>961</v>
+      </c>
+      <c r="D7" s="12" t="s">
         <v>955</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>949</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>29</v>
@@ -13315,15 +13395,15 @@
         <v>37</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="12" t="s">
@@ -13339,10 +13419,10 @@
     </row>
     <row r="9" spans="2:8" ht="409.5">
       <c r="B9" s="12" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="12" t="s">
@@ -13358,13 +13438,13 @@
     </row>
     <row r="10" spans="2:8" ht="409.5">
       <c r="B10" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -13379,55 +13459,55 @@
     </row>
     <row r="11" spans="2:8" ht="275.45">
       <c r="B11" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="H11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="188.45">
       <c r="B12" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="H12" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="409.5">
       <c r="B13" s="12" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
@@ -13436,7 +13516,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="H13" s="42"/>
     </row>
@@ -13454,36 +13534,36 @@
   <sheetData>
     <row r="2" spans="2:8" ht="362.45">
       <c r="B2" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>948</v>
+        <v>954</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>950</v>
+        <v>956</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>951</v>
+        <v>957</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="304.5">
       <c r="B3" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>952</v>
+        <v>958</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>29</v>
@@ -13495,18 +13575,18 @@
         <v>31</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="409.5">
       <c r="B4" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>954</v>
+        <v>960</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>29</v>
@@ -13518,18 +13598,18 @@
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="409.5">
       <c r="B5" s="12" t="s">
-        <v>947</v>
+        <v>953</v>
       </c>
       <c r="C5" s="16" t="s">
+        <v>961</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>955</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>949</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13541,15 +13621,15 @@
         <v>37</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>953</v>
+        <v>959</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>957</v>
+        <v>963</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="12" t="s">
@@ -13565,10 +13645,10 @@
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>956</v>
+        <v>962</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>958</v>
+        <v>964</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="12" t="s">
@@ -13584,13 +13664,13 @@
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>960</v>
+        <v>966</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>29</v>
@@ -13605,55 +13685,55 @@
     </row>
     <row r="9" spans="2:8" ht="275.45">
       <c r="B9" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>961</v>
+        <v>967</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>962</v>
+        <v>968</v>
       </c>
       <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="188.45">
       <c r="B10" s="12" t="s">
-        <v>959</v>
+        <v>965</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>963</v>
+        <v>969</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>964</v>
+        <v>970</v>
       </c>
       <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="409.5">
       <c r="B11" s="12" t="s">
-        <v>965</v>
+        <v>971</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>949</v>
+        <v>955</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
@@ -13662,7 +13742,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>967</v>
+        <v>973</v>
       </c>
       <c r="H11" s="42"/>
     </row>

--- a/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
+++ b/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/GenIA/Normativo/LexIA_Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="354" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76C6455B-6FAC-4842-8952-D3366FFEB454}"/>
+  <xr:revisionPtr revIDLastSave="402" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{095319E4-5ABE-44D7-BD13-9D5AB584B8F2}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2494" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="989">
   <si>
     <t>Dia</t>
   </si>
@@ -2920,6 +2920,56 @@
   </si>
   <si>
     <t>Modifican la Resolución SBS N° 04131-2025 y el Reglamento de Notificación vía Casilla Electrónica de la SBS</t>
+  </si>
+  <si>
+    <t>Nº 683-2026-MDB</t>
+  </si>
+  <si>
+    <t>Ordenanza que regula el procedimiento de autorización para la ubicación de elementos de publicidad exterior en el distrito de Barranco</t>
+  </si>
+  <si>
+    <t>RESOLUCIÓN SBS</t>
+  </si>
+  <si>
+    <t>N° 02051-2026</t>
+  </si>
+  <si>
+    <t>Autorizan difusión en consulta pública del proyecto normativo que establece
+disposiciones prudenciales para las empresas del sistema financiero y de
+seguros autorizadas a contar con una línea de negocios adicional y que modifica el
+Manual de Contabilidad para las Carteras Administradas, el Manual de Contabilidad
+para las Empresas del Sistema Financiero y el Plan de Cuentas para las Empresas del
+Sistema Asegurador</t>
+  </si>
+  <si>
+    <t>N° 02027-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La SBS modifica el Reglamento de Notificación vía Casilla Electrónica (SISNE) para incorporar dentro de su alcance a las personas naturales y jurídicas sujetas a procedimientos tributarios y de ejecución coactiva iniciados por la Superintendencia. Asimismo, establece reglas específicas para la eficacia de las notificaciones electrónicas en materia tributaria, precisando que determinadas medidas cautelares podrán surtir efecto desde su depósito en la casilla electrónica. La medida busca fortalecer la celeridad, inmediatez y eficacia de las comunicaciones y actuaciones administrativas de la SBS. </t>
+  </si>
+  <si>
+    <t>N° 02038-2026</t>
+  </si>
+  <si>
+    <t>Proyecto para actualizar el requerimiento de patrimonio efectivo por riesgo de mercado</t>
+  </si>
+  <si>
+    <t>N° 02037-2026</t>
+  </si>
+  <si>
+    <t>Proyecto que modifica reglamento para la gestión del riesgo de tasa de interés del libro bancario</t>
+  </si>
+  <si>
+    <t>N° 00392-2026/MDSA</t>
+  </si>
+  <si>
+    <t>Ordenanza que regula las disposiciones técnicas y procedimientos administrativos de autorización para la ubicación de elementos de publicidad exterior en el distrito de Santa Anita</t>
+  </si>
+  <si>
+    <t>N° 741/MDC</t>
+  </si>
+  <si>
+    <t>Ordenanza Municipal que Regula las Autorizaciones para la Ubicación de Elementos de Publicidad Exterior en el distrito de Comas</t>
   </si>
   <si>
     <t>IDENTIFICÓ LA NORMA DE INTERÉS</t>
@@ -3015,7 +3065,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3072,6 +3122,11 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -3177,7 +3232,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3307,6 +3362,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13255,6 +13320,146 @@
         <v>947</v>
       </c>
     </row>
+    <row r="467" spans="1:6" ht="15">
+      <c r="A467" s="3">
+        <v>46249</v>
+      </c>
+      <c r="B467" t="s">
+        <v>69</v>
+      </c>
+      <c r="C467" t="s">
+        <v>948</v>
+      </c>
+      <c r="D467" t="s">
+        <v>29</v>
+      </c>
+      <c r="E467" t="s">
+        <v>840</v>
+      </c>
+      <c r="F467" s="4" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6" ht="115.5">
+      <c r="A468" s="51">
+        <v>46251</v>
+      </c>
+      <c r="B468" s="52" t="s">
+        <v>950</v>
+      </c>
+      <c r="C468" s="50" t="s">
+        <v>951</v>
+      </c>
+      <c r="D468" s="50" t="s">
+        <v>29</v>
+      </c>
+      <c r="E468" s="50" t="s">
+        <v>835</v>
+      </c>
+      <c r="F468" s="48" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
+      <c r="A469" s="3">
+        <v>46247</v>
+      </c>
+      <c r="B469" t="s">
+        <v>950</v>
+      </c>
+      <c r="C469" t="s">
+        <v>953</v>
+      </c>
+      <c r="D469" t="s">
+        <v>29</v>
+      </c>
+      <c r="E469" t="s">
+        <v>840</v>
+      </c>
+      <c r="F469" s="4" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
+      <c r="A470" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B470" t="s">
+        <v>950</v>
+      </c>
+      <c r="C470" t="s">
+        <v>955</v>
+      </c>
+      <c r="D470" t="s">
+        <v>29</v>
+      </c>
+      <c r="E470" t="s">
+        <v>835</v>
+      </c>
+      <c r="F470" s="4" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
+      <c r="A471" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B471" t="s">
+        <v>950</v>
+      </c>
+      <c r="C471" t="s">
+        <v>957</v>
+      </c>
+      <c r="D471" t="s">
+        <v>29</v>
+      </c>
+      <c r="E471" t="s">
+        <v>835</v>
+      </c>
+      <c r="F471" s="4" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6" ht="15">
+      <c r="A472" s="3">
+        <v>46254</v>
+      </c>
+      <c r="B472" t="s">
+        <v>69</v>
+      </c>
+      <c r="C472" s="53" t="s">
+        <v>959</v>
+      </c>
+      <c r="D472" t="s">
+        <v>29</v>
+      </c>
+      <c r="E472" t="s">
+        <v>30</v>
+      </c>
+      <c r="F472" s="4" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
+      <c r="A473" s="3">
+        <v>46252</v>
+      </c>
+      <c r="B473" t="s">
+        <v>69</v>
+      </c>
+      <c r="C473" t="s">
+        <v>961</v>
+      </c>
+      <c r="D473" t="s">
+        <v>29</v>
+      </c>
+      <c r="E473" t="s">
+        <v>30</v>
+      </c>
+      <c r="F473" s="4" t="s">
+        <v>962</v>
+      </c>
+    </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
     <row r="1048574" ht="12.75" customHeight="1"/>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -13264,7 +13469,7 @@
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C28 C49:C414 C1 C420 C426:C1048576">
+  <conditionalFormatting sqref="C3:C28 C49:C414 C1 C420 C426:C466 C468:C471 C473:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13279,7 +13484,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="D2" s="34" t="s">
-        <v>948</v>
+        <v>963</v>
       </c>
       <c r="E2" s="34"/>
     </row>
@@ -13288,10 +13493,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>949</v>
+        <v>964</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>950</v>
+        <v>965</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>24</v>
@@ -13300,44 +13505,44 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>951</v>
+        <v>966</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>952</v>
+        <v>967</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="362.45">
       <c r="B4" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="304.5">
       <c r="B5" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13349,18 +13554,18 @@
         <v>31</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>29</v>
@@ -13372,18 +13577,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>29</v>
@@ -13395,15 +13600,15 @@
         <v>37</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="12" t="s">
@@ -13419,10 +13624,10 @@
     </row>
     <row r="9" spans="2:8" ht="409.5">
       <c r="B9" s="12" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="12" t="s">
@@ -13438,13 +13643,13 @@
     </row>
     <row r="10" spans="2:8" ht="409.5">
       <c r="B10" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -13459,55 +13664,55 @@
     </row>
     <row r="11" spans="2:8" ht="275.45">
       <c r="B11" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="H11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="188.45">
       <c r="B12" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="H12" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="409.5">
       <c r="B13" s="12" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
@@ -13516,7 +13721,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
       <c r="H13" s="42"/>
     </row>
@@ -13534,36 +13739,36 @@
   <sheetData>
     <row r="2" spans="2:8" ht="362.45">
       <c r="B2" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>954</v>
+        <v>969</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>956</v>
+        <v>971</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>957</v>
+        <v>972</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="304.5">
       <c r="B3" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>958</v>
+        <v>973</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>29</v>
@@ -13575,18 +13780,18 @@
         <v>31</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="409.5">
       <c r="B4" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>960</v>
+        <v>975</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>29</v>
@@ -13598,18 +13803,18 @@
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="409.5">
       <c r="B5" s="12" t="s">
-        <v>953</v>
+        <v>968</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>961</v>
+        <v>976</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13621,15 +13826,15 @@
         <v>37</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>959</v>
+        <v>974</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>963</v>
+        <v>978</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="12" t="s">
@@ -13645,10 +13850,10 @@
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>962</v>
+        <v>977</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>964</v>
+        <v>979</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="12" t="s">
@@ -13664,13 +13869,13 @@
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>966</v>
+        <v>981</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>29</v>
@@ -13685,55 +13890,55 @@
     </row>
     <row r="9" spans="2:8" ht="275.45">
       <c r="B9" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>967</v>
+        <v>982</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>968</v>
+        <v>983</v>
       </c>
       <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="188.45">
       <c r="B10" s="12" t="s">
-        <v>965</v>
+        <v>980</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>969</v>
+        <v>984</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>970</v>
+        <v>985</v>
       </c>
       <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="409.5">
       <c r="B11" s="12" t="s">
-        <v>971</v>
+        <v>986</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>972</v>
+        <v>987</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>955</v>
+        <v>970</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
@@ -13742,7 +13947,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>973</v>
+        <v>988</v>
       </c>
       <c r="H11" s="42"/>
     </row>

--- a/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
+++ b/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/GenIA/Normativo/LexIA_Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="402" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{095319E4-5ABE-44D7-BD13-9D5AB584B8F2}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD013B4E-E4BF-4C05-B794-D4C3A186EC3B}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2529" uniqueCount="989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1005">
   <si>
     <t>Dia</t>
   </si>
@@ -2970,6 +2970,54 @@
   </si>
   <si>
     <t>Ordenanza Municipal que Regula las Autorizaciones para la Ubicación de Elementos de Publicidad Exterior en el distrito de Comas</t>
+  </si>
+  <si>
+    <t>Nº 0020-2026-BCRP</t>
+  </si>
+  <si>
+    <t>Disposiciones de encaje en moneda extranjera</t>
+  </si>
+  <si>
+    <t>Nº 119-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el estado de emergencia en los distritos de Chumpi, Coracora, Pullo y Upahuacho de la provincia de Parinacochas y el distrito de Carapo en la provincia de Huanca Sancos del departamento de Ayacucho, por impacto de daños a consecuencia de movimientos sísmicos</t>
+  </si>
+  <si>
+    <t>N° 118-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el Estado de Emergencia en el distrito de Atico de la provincia de Caravelí del departamento de Arequipa, en el distrito de Ilo de la provincia de Ilo del departamento de Moquegua y en el distrito de Cairani de la provincia de Candarave del departamento de Tacna, por impacto de daños a consecuencia de intensas precipitaciones pluviales y vientos fuertes asociados a la presencia de la DANA Aníba</t>
+  </si>
+  <si>
+    <t>Nº 117-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el Estado de Emergencia en los distritos de Villa El Salvador y de Villa María del Triunfo de la provincia y departamento de Lima, por impacto de daños a consecuencia de aniegos por lloviznas persistentes</t>
+  </si>
+  <si>
+    <t>N° 012-2026-PRODUCE</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara en emergencia los subsectores pesca y acuicultura</t>
+  </si>
+  <si>
+    <t>N° 02104-2026</t>
+  </si>
+  <si>
+    <t>Modifican el Manual de Contabilidad para las Empresas del Sistema Financiero, el Plan de Cuentas para las Empresas del Sistema Asegurador y el Manual de Contabilidad para las Administradoras Privadas de Fondos de Pensiones</t>
+  </si>
+  <si>
+    <t>N° 02116-2026</t>
+  </si>
+  <si>
+    <t>Modifican el Reglamento de Canales Complementarios de Atención al Público de las Empresas del Sistema Financiero y de las Empresas Emisoras de Dinero Electrónico</t>
+  </si>
+  <si>
+    <t>N° 754-MSB</t>
+  </si>
+  <si>
+    <t>Ordenanza que aprueba el Reglamento de Licencias de Funcionamiento y Autorizaciones Comerciales de la Municipalidad de San Borja</t>
   </si>
   <si>
     <t>IDENTIFICÓ LA NORMA DE INTERÉS</t>
@@ -13460,6 +13508,166 @@
         <v>962</v>
       </c>
     </row>
+    <row r="474" spans="1:6">
+      <c r="A474" s="3">
+        <v>46256</v>
+      </c>
+      <c r="B474" t="s">
+        <v>49</v>
+      </c>
+      <c r="C474" t="s">
+        <v>963</v>
+      </c>
+      <c r="D474" t="s">
+        <v>29</v>
+      </c>
+      <c r="E474" t="s">
+        <v>835</v>
+      </c>
+      <c r="F474" s="4" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
+      <c r="A475" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B475" t="s">
+        <v>46</v>
+      </c>
+      <c r="C475" t="s">
+        <v>965</v>
+      </c>
+      <c r="D475" t="s">
+        <v>29</v>
+      </c>
+      <c r="E475" t="s">
+        <v>30</v>
+      </c>
+      <c r="F475" s="4" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
+      <c r="A476" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B476" t="s">
+        <v>46</v>
+      </c>
+      <c r="C476" t="s">
+        <v>967</v>
+      </c>
+      <c r="D476" t="s">
+        <v>29</v>
+      </c>
+      <c r="E476" t="s">
+        <v>30</v>
+      </c>
+      <c r="F476" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
+      <c r="A477" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B477" t="s">
+        <v>46</v>
+      </c>
+      <c r="C477" t="s">
+        <v>969</v>
+      </c>
+      <c r="D477" t="s">
+        <v>29</v>
+      </c>
+      <c r="E477" t="s">
+        <v>840</v>
+      </c>
+      <c r="F477" s="4" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
+      <c r="A478" s="3">
+        <v>46257</v>
+      </c>
+      <c r="B478" t="s">
+        <v>46</v>
+      </c>
+      <c r="C478" t="s">
+        <v>971</v>
+      </c>
+      <c r="D478" t="s">
+        <v>29</v>
+      </c>
+      <c r="E478" t="s">
+        <v>30</v>
+      </c>
+      <c r="F478" s="4" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
+      <c r="A479" s="3">
+        <v>46258</v>
+      </c>
+      <c r="B479" t="s">
+        <v>950</v>
+      </c>
+      <c r="C479" t="s">
+        <v>973</v>
+      </c>
+      <c r="D479" t="s">
+        <v>29</v>
+      </c>
+      <c r="E479" t="s">
+        <v>835</v>
+      </c>
+      <c r="F479" s="4" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
+      <c r="A480" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B480" t="s">
+        <v>950</v>
+      </c>
+      <c r="C480" t="s">
+        <v>975</v>
+      </c>
+      <c r="D480" t="s">
+        <v>29</v>
+      </c>
+      <c r="E480" t="s">
+        <v>30</v>
+      </c>
+      <c r="F480" s="4" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6">
+      <c r="A481" s="3">
+        <v>46260</v>
+      </c>
+      <c r="B481" t="s">
+        <v>69</v>
+      </c>
+      <c r="C481" t="s">
+        <v>977</v>
+      </c>
+      <c r="D481" t="s">
+        <v>29</v>
+      </c>
+      <c r="E481" t="s">
+        <v>30</v>
+      </c>
+      <c r="F481" s="4" t="s">
+        <v>978</v>
+      </c>
+    </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
     <row r="1048574" ht="12.75" customHeight="1"/>
     <row r="1048575" ht="12.75" customHeight="1"/>
@@ -13484,7 +13692,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="D2" s="34" t="s">
-        <v>963</v>
+        <v>979</v>
       </c>
       <c r="E2" s="34"/>
     </row>
@@ -13493,10 +13701,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>964</v>
+        <v>980</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>965</v>
+        <v>981</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>24</v>
@@ -13505,44 +13713,44 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>966</v>
+        <v>982</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>967</v>
+        <v>983</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="362.45">
       <c r="B4" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="304.5">
       <c r="B5" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13554,18 +13762,18 @@
         <v>31</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>29</v>
@@ -13577,18 +13785,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>29</v>
@@ -13600,15 +13808,15 @@
         <v>37</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="12" t="s">
@@ -13624,10 +13832,10 @@
     </row>
     <row r="9" spans="2:8" ht="409.5">
       <c r="B9" s="12" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="12" t="s">
@@ -13643,13 +13851,13 @@
     </row>
     <row r="10" spans="2:8" ht="409.5">
       <c r="B10" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -13664,56 +13872,56 @@
     </row>
     <row r="11" spans="2:8" ht="275.45">
       <c r="B11" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="H11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="188.45">
       <c r="B12" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="H12" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="409.5">
       <c r="B13" s="12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>987</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>970</v>
-      </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
       </c>
@@ -13721,7 +13929,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>988</v>
+        <v>1004</v>
       </c>
       <c r="H13" s="42"/>
     </row>
@@ -13739,36 +13947,36 @@
   <sheetData>
     <row r="2" spans="2:8" ht="362.45">
       <c r="B2" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>969</v>
+        <v>985</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>971</v>
+        <v>987</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>972</v>
+        <v>988</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="304.5">
       <c r="B3" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>973</v>
+        <v>989</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>29</v>
@@ -13780,18 +13988,18 @@
         <v>31</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="409.5">
       <c r="B4" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>975</v>
+        <v>991</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>29</v>
@@ -13803,18 +14011,18 @@
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="409.5">
       <c r="B5" s="12" t="s">
-        <v>968</v>
+        <v>984</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>976</v>
+        <v>992</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13826,15 +14034,15 @@
         <v>37</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>974</v>
+        <v>990</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>978</v>
+        <v>994</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="12" t="s">
@@ -13850,10 +14058,10 @@
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>977</v>
+        <v>993</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>979</v>
+        <v>995</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="12" t="s">
@@ -13869,13 +14077,13 @@
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>981</v>
+        <v>997</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>29</v>
@@ -13890,56 +14098,56 @@
     </row>
     <row r="9" spans="2:8" ht="275.45">
       <c r="B9" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>982</v>
+        <v>998</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>983</v>
+        <v>999</v>
       </c>
       <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="188.45">
       <c r="B10" s="12" t="s">
-        <v>980</v>
+        <v>996</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>984</v>
+        <v>1000</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>970</v>
+        <v>986</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>985</v>
+        <v>1001</v>
       </c>
       <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="409.5">
       <c r="B11" s="12" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>986</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>987</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>970</v>
-      </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
       </c>
@@ -13947,7 +14155,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>988</v>
+        <v>1004</v>
       </c>
       <c r="H11" s="42"/>
     </row>

--- a/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
+++ b/LexIA_Diario/Comparativo de identificación de normas VF (1).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://interbankpe-my.sharepoint.com/personal/shernandez2_intercorp_com_pe/Documents/PLAFT/GenIA/Normativo/LexIA_Diario/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD013B4E-E4BF-4C05-B794-D4C3A186EC3B}"/>
+  <xr:revisionPtr revIDLastSave="531" documentId="11_FF9E2F5B496FDA3AB52BB0B2B6FDBBEC0357B1A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E48F9C1E-50FD-44CB-BF18-B32E140B0745}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="500" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2569" uniqueCount="1005">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2624" uniqueCount="1027">
   <si>
     <t>Dia</t>
   </si>
@@ -3018,6 +3018,79 @@
   </si>
   <si>
     <t>Ordenanza que aprueba el Reglamento de Licencias de Funcionamiento y Autorizaciones Comerciales de la Municipalidad de San Borja</t>
+  </si>
+  <si>
+    <t>N° 02060-2026</t>
+  </si>
+  <si>
+    <t>Autorizan la organización de una empresa emisora de dinero electrónico bajo la
+denominación social de “OneKey Perú EEDE S.A.”</t>
+  </si>
+  <si>
+    <t>Nº 02133-2026</t>
+  </si>
+  <si>
+    <t>Modifican el Reglamento de Autorización de Empresas y Representantes de los Sistemas 
+Financiero y de Seguros, aprobado por la Resolución SBS N° 211-2021</t>
+  </si>
+  <si>
+    <t>Separata Especial Marco Macroeconómico Multianual 2027-2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolución SMV </t>
+  </si>
+  <si>
+    <t>N° 012-2026-SMV/01</t>
+  </si>
+  <si>
+    <t>Modifican el Reglamento de Oferta Pública Primaria y de Venta de Valores Mobiliarios</t>
+  </si>
+  <si>
+    <t>Nº 120-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el Estado de Emergencia en el distrito de Encañada de la provincia de Cajamarca; en el distrito de Cachachi de la provincia de Cajabamba; en los distritos de Sorochuco y Huasmín de la provincia de Celendín; en los distritos de Hualgayoc y Bambamarca de la provincia de Hualgayoc; en los distritos de San Ignacio, San José de Lourdes y Namballe de la provincia de San Ignacio y en el distrito de Bellavista de la provincia de Jaén del departamento de Cajamarca</t>
+  </si>
+  <si>
+    <t>Nº 121-2026-PCM</t>
+  </si>
+  <si>
+    <t>Nº 123-2026-PCM</t>
+  </si>
+  <si>
+    <t>Nº 124-2026-PCM</t>
+  </si>
+  <si>
+    <t>Decreto Supremo que declara el Estado de Emergencia en varios distritos de algunas provincias de los departamentos de Amazonas, Áncash, Apurímac, Arequipa,
+Ayacucho, Cajamarca, Huancavelica, Huánuco, Ica, Junín, La Libertad,Lambayeque, Lima, Loreto, Madre de Dios, Moquegua, Pasco, Piura, San Martín, Tacna, Tumbes, Ucayali y la Provincia Constitucional del Callao, por peligro
+inminente ante intensas precipitaciones pluviales asociadas al Fenómeno El Niño
+2026-2027</t>
+  </si>
+  <si>
+    <t>Resolución INEI</t>
+  </si>
+  <si>
+    <t>Nº 194-2026-INEI</t>
+  </si>
+  <si>
+    <t>Aprueban Índice de Precios al Consumidor a Nivel Nacional e Índice de Precios al
+Consumidor de Lima Metropolitana correspondientes al mes de agosto de 2026</t>
+  </si>
+  <si>
+    <t>Nº 195-2026-INEI</t>
+  </si>
+  <si>
+    <t>Aprueban Índice de Precios al Por Mayor a Nivel Nacional, correspondiente al mes de agosto de 2026</t>
+  </si>
+  <si>
+    <t>Circular BCRP</t>
+  </si>
+  <si>
+    <t>N° 0021-2026-BCRP</t>
+  </si>
+  <si>
+    <t>Índice de reajuste diario a que se refiere el artículo 240° de la Ley General del Sistema Financiero y del Sistema de Seguros, correspondiente al mes de setiembre de
+2026</t>
   </si>
   <si>
     <t>IDENTIFICÓ LA NORMA DE INTERÉS</t>
@@ -3113,7 +3186,7 @@
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="167" formatCode="dd/mm/yy"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3176,8 +3249,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3199,6 +3278,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3280,7 +3371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -3419,7 +3510,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13368,23 +13479,23 @@
         <v>947</v>
       </c>
     </row>
-    <row r="467" spans="1:6" ht="15">
-      <c r="A467" s="3">
+    <row r="467" spans="1:6" s="58" customFormat="1" ht="15">
+      <c r="A467" s="61">
         <v>46249</v>
       </c>
-      <c r="B467" t="s">
+      <c r="B467" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C467" t="s">
+      <c r="C467" s="58" t="s">
         <v>948</v>
       </c>
-      <c r="D467" t="s">
-        <v>29</v>
-      </c>
-      <c r="E467" t="s">
+      <c r="D467" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E467" s="58" t="s">
         <v>840</v>
       </c>
-      <c r="F467" s="4" t="s">
+      <c r="F467" s="53" t="s">
         <v>949</v>
       </c>
     </row>
@@ -13468,43 +13579,43 @@
         <v>958</v>
       </c>
     </row>
-    <row r="472" spans="1:6" ht="15">
-      <c r="A472" s="3">
+    <row r="472" spans="1:6" s="58" customFormat="1" ht="15">
+      <c r="A472" s="61">
         <v>46254</v>
       </c>
-      <c r="B472" t="s">
+      <c r="B472" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C472" s="53" t="s">
+      <c r="C472" s="59" t="s">
         <v>959</v>
       </c>
-      <c r="D472" t="s">
-        <v>29</v>
-      </c>
-      <c r="E472" t="s">
-        <v>30</v>
-      </c>
-      <c r="F472" s="4" t="s">
+      <c r="D472" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E472" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="F472" s="53" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="473" spans="1:6">
-      <c r="A473" s="3">
+    <row r="473" spans="1:6" s="58" customFormat="1">
+      <c r="A473" s="61">
         <v>46252</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="C473" t="s">
+      <c r="C473" s="58" t="s">
         <v>961</v>
       </c>
-      <c r="D473" t="s">
-        <v>29</v>
-      </c>
-      <c r="E473" t="s">
-        <v>30</v>
-      </c>
-      <c r="F473" s="4" t="s">
+      <c r="D473" s="58" t="s">
+        <v>29</v>
+      </c>
+      <c r="E473" s="58" t="s">
+        <v>30</v>
+      </c>
+      <c r="F473" s="53" t="s">
         <v>962</v>
       </c>
     </row>
@@ -13664,8 +13775,228 @@
       <c r="E481" t="s">
         <v>30</v>
       </c>
-      <c r="F481" s="4" t="s">
+      <c r="F481" s="60" t="s">
         <v>978</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6" ht="29.25">
+      <c r="A482" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B482" t="s">
+        <v>950</v>
+      </c>
+      <c r="C482" t="s">
+        <v>979</v>
+      </c>
+      <c r="D482" t="s">
+        <v>29</v>
+      </c>
+      <c r="E482" t="s">
+        <v>30</v>
+      </c>
+      <c r="F482" s="45" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6" ht="43.5">
+      <c r="A483" s="3">
+        <v>46261</v>
+      </c>
+      <c r="B483" t="s">
+        <v>950</v>
+      </c>
+      <c r="C483" t="s">
+        <v>981</v>
+      </c>
+      <c r="D483" t="s">
+        <v>29</v>
+      </c>
+      <c r="E483" t="s">
+        <v>30</v>
+      </c>
+      <c r="F483" s="45" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6">
+      <c r="A484" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B484" t="s">
+        <v>983</v>
+      </c>
+      <c r="C484" t="s">
+        <v>983</v>
+      </c>
+      <c r="D484" t="s">
+        <v>29</v>
+      </c>
+      <c r="E484" t="s">
+        <v>30</v>
+      </c>
+      <c r="F484" s="4" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6">
+      <c r="A485" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B485" t="s">
+        <v>984</v>
+      </c>
+      <c r="C485" t="s">
+        <v>985</v>
+      </c>
+      <c r="D485" t="s">
+        <v>29</v>
+      </c>
+      <c r="E485" t="s">
+        <v>840</v>
+      </c>
+      <c r="F485" s="4" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6" ht="101.25">
+      <c r="A486" s="54">
+        <v>46262</v>
+      </c>
+      <c r="B486" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C486" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="D486" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E486" s="55" t="s">
+        <v>840</v>
+      </c>
+      <c r="F486" s="49" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6" ht="50.25">
+      <c r="A487" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B487" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C487" s="56" t="s">
+        <v>989</v>
+      </c>
+      <c r="D487" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E487" t="s">
+        <v>840</v>
+      </c>
+      <c r="F487" s="56" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6" ht="24.75">
+      <c r="A488" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B488" s="55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C488" s="57" t="s">
+        <v>990</v>
+      </c>
+      <c r="D488" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E488" t="s">
+        <v>840</v>
+      </c>
+      <c r="F488" s="57" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6" ht="115.5">
+      <c r="A489" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B489" t="s">
+        <v>46</v>
+      </c>
+      <c r="C489" s="56" t="s">
+        <v>991</v>
+      </c>
+      <c r="D489" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E489" t="s">
+        <v>840</v>
+      </c>
+      <c r="F489" s="45" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6" ht="29.25">
+      <c r="A490" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B490" t="s">
+        <v>993</v>
+      </c>
+      <c r="C490" s="57" t="s">
+        <v>994</v>
+      </c>
+      <c r="D490" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E490" t="s">
+        <v>840</v>
+      </c>
+      <c r="F490" s="45" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6" ht="15">
+      <c r="A491" s="3">
+        <v>46266</v>
+      </c>
+      <c r="B491" t="s">
+        <v>993</v>
+      </c>
+      <c r="C491" s="57" t="s">
+        <v>996</v>
+      </c>
+      <c r="D491" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E491" t="s">
+        <v>30</v>
+      </c>
+      <c r="F491" s="4" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6" ht="57.75">
+      <c r="A492" s="3">
+        <v>46267</v>
+      </c>
+      <c r="B492" t="s">
+        <v>998</v>
+      </c>
+      <c r="C492" s="57" t="s">
+        <v>999</v>
+      </c>
+      <c r="D492" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="E492" t="s">
+        <v>30</v>
+      </c>
+      <c r="F492" s="45" t="s">
+        <v>1000</v>
       </c>
     </row>
     <row r="1048573" ht="12.75" customHeight="1"/>
@@ -13673,11 +14004,11 @@
     <row r="1048575" ht="12.75" customHeight="1"/>
     <row r="1048576" ht="12.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:F8" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A1:F492" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="C2">
     <cfRule type="duplicateValues" dxfId="1" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C3:C28 C49:C414 C1 C420 C426:C466 C468:C471 C473:C1048576">
+  <conditionalFormatting sqref="C3:C28 C49:C414 C1 C420 C426:C466 C468:C471 C473:C486 C493:C1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -13692,7 +14023,7 @@
   <sheetData>
     <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="D2" s="34" t="s">
-        <v>979</v>
+        <v>1001</v>
       </c>
       <c r="E2" s="34"/>
     </row>
@@ -13701,10 +14032,10 @@
         <v>21</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>980</v>
+        <v>1002</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>981</v>
+        <v>1003</v>
       </c>
       <c r="E3" s="36" t="s">
         <v>24</v>
@@ -13713,44 +14044,44 @@
         <v>25</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>982</v>
+        <v>1004</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>983</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="362.45">
       <c r="B4" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C4" s="37" t="s">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="D4" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>987</v>
+        <v>1009</v>
       </c>
       <c r="H4" s="38" t="s">
-        <v>988</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="304.5">
       <c r="B5" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C5" s="39" t="s">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -13762,18 +14093,18 @@
         <v>31</v>
       </c>
       <c r="H5" s="40" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>991</v>
+        <v>1013</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>29</v>
@@ -13785,18 +14116,18 @@
         <v>34</v>
       </c>
       <c r="H6" s="41" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>992</v>
+        <v>1014</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E7" s="12" t="s">
         <v>29</v>
@@ -13808,15 +14139,15 @@
         <v>37</v>
       </c>
       <c r="H7" s="41" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="D8" s="42"/>
       <c r="E8" s="12" t="s">
@@ -13832,10 +14163,10 @@
     </row>
     <row r="9" spans="2:8" ht="409.5">
       <c r="B9" s="12" t="s">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>995</v>
+        <v>1017</v>
       </c>
       <c r="D9" s="42"/>
       <c r="E9" s="12" t="s">
@@ -13851,13 +14182,13 @@
     </row>
     <row r="10" spans="2:8" ht="409.5">
       <c r="B10" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>997</v>
+        <v>1019</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>29</v>
@@ -13872,55 +14203,55 @@
     </row>
     <row r="11" spans="2:8" ht="275.45">
       <c r="B11" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>998</v>
+        <v>1020</v>
       </c>
       <c r="D11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="H11" s="42"/>
     </row>
     <row r="12" spans="2:8" ht="188.45">
       <c r="B12" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>1000</v>
+        <v>1022</v>
       </c>
       <c r="D12" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="40" t="s">
-        <v>1001</v>
+        <v>1023</v>
       </c>
       <c r="H12" s="42"/>
     </row>
     <row r="13" spans="2:8" ht="409.5">
       <c r="B13" s="12" t="s">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>1003</v>
+        <v>1025</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E13" s="12" t="s">
         <v>29</v>
@@ -13929,7 +14260,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="40" t="s">
-        <v>1004</v>
+        <v>1026</v>
       </c>
       <c r="H13" s="42"/>
     </row>
@@ -13947,36 +14278,36 @@
   <sheetData>
     <row r="2" spans="2:8" ht="362.45">
       <c r="B2" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>985</v>
+        <v>1007</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>987</v>
+        <v>1009</v>
       </c>
       <c r="H2" s="38" t="s">
-        <v>988</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="304.5">
       <c r="B3" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C3" s="39" t="s">
-        <v>989</v>
+        <v>1011</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>29</v>
@@ -13988,18 +14319,18 @@
         <v>31</v>
       </c>
       <c r="H3" s="40" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="409.5">
       <c r="B4" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>991</v>
+        <v>1013</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>29</v>
@@ -14011,18 +14342,18 @@
         <v>34</v>
       </c>
       <c r="H4" s="41" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="409.5">
       <c r="B5" s="12" t="s">
-        <v>984</v>
+        <v>1006</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>992</v>
+        <v>1014</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>29</v>
@@ -14034,15 +14365,15 @@
         <v>37</v>
       </c>
       <c r="H5" s="41" t="s">
-        <v>990</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="409.5">
       <c r="B6" s="12" t="s">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>994</v>
+        <v>1016</v>
       </c>
       <c r="D6" s="42"/>
       <c r="E6" s="12" t="s">
@@ -14058,10 +14389,10 @@
     </row>
     <row r="7" spans="2:8" ht="409.5">
       <c r="B7" s="12" t="s">
-        <v>993</v>
+        <v>1015</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>995</v>
+        <v>1017</v>
       </c>
       <c r="D7" s="42"/>
       <c r="E7" s="12" t="s">
@@ -14077,13 +14408,13 @@
     </row>
     <row r="8" spans="2:8" ht="409.5">
       <c r="B8" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>997</v>
+        <v>1019</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>29</v>
@@ -14098,55 +14429,55 @@
     </row>
     <row r="9" spans="2:8" ht="275.45">
       <c r="B9" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>998</v>
+        <v>1020</v>
       </c>
       <c r="D9" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G9" s="40" t="s">
-        <v>999</v>
+        <v>1021</v>
       </c>
       <c r="H9" s="42"/>
     </row>
     <row r="10" spans="2:8" ht="188.45">
       <c r="B10" s="12" t="s">
-        <v>996</v>
+        <v>1018</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1000</v>
+        <v>1022</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="40" t="s">
-        <v>1001</v>
+        <v>1023</v>
       </c>
       <c r="H10" s="42"/>
     </row>
     <row r="11" spans="2:8" ht="409.5">
       <c r="B11" s="12" t="s">
-        <v>1002</v>
+        <v>1024</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>1003</v>
+        <v>1025</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>986</v>
+        <v>1008</v>
       </c>
       <c r="E11" s="12" t="s">
         <v>29</v>
@@ -14155,7 +14486,7 @@
         <v>30</v>
       </c>
       <c r="G11" s="40" t="s">
-        <v>1004</v>
+        <v>1026</v>
       </c>
       <c r="H11" s="42"/>
     </row>
